--- a/database.xlsx
+++ b/database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyServer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75AB7BF5-A936-427F-823F-5CBC9AB5F0C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F24332D0-AFDD-48D6-A416-B8B6D9036A2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17370" yWindow="3795" windowWidth="13215" windowHeight="15240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17850" yWindow="3270" windowWidth="13215" windowHeight="15240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="33">
   <si>
     <t>code</t>
   </si>
@@ -135,17 +135,32 @@
   <si>
     <t>17.11.2025 Уехала экспрессом сразу клиенту</t>
   </si>
+  <si>
+    <t>09.14.2024</t>
+  </si>
+  <si>
+    <t>10.12.2025 приехала в ремонт. Инкассаторы вставили задом наперед 
+11.12.2025 отремонтирована, готова к отправке</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -248,43 +263,46 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -293,16 +311,19 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5832,7 +5853,7 @@
         <v>45616</v>
       </c>
     </row>
-    <row r="497" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A497" s="1">
         <v>25662</v>
       </c>
@@ -5843,45 +5864,56 @@
         <v>45616</v>
       </c>
     </row>
-    <row r="498" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B498" s="14"/>
-    </row>
-    <row r="505" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A498" s="1">
+        <v>24969</v>
+      </c>
+      <c r="B498" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C498" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D498" s="22" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="505" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A505" s="1">
         <v>100297</v>
       </c>
     </row>
-    <row r="506" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A506" s="1">
         <v>100298</v>
       </c>
     </row>
-    <row r="507" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A507" s="1">
         <v>100299</v>
       </c>
     </row>
-    <row r="508" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A508" s="1">
         <v>100300</v>
       </c>
     </row>
-    <row r="509" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A509" s="1">
         <v>100301</v>
       </c>
     </row>
-    <row r="510" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A510" s="1">
         <v>100302</v>
       </c>
     </row>
-    <row r="511" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A511" s="1">
         <v>100303</v>
       </c>
     </row>
-    <row r="512" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A512" s="1">
         <v>100304</v>
       </c>

--- a/database.xlsx
+++ b/database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyServer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F24332D0-AFDD-48D6-A416-B8B6D9036A2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{511B6B25-0B1E-4864-AEA4-4768EE13BD51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17850" yWindow="3270" windowWidth="13215" windowHeight="15240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="20910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="34">
   <si>
     <t>code</t>
   </si>
@@ -142,17 +142,28 @@
     <t>10.12.2025 приехала в ремонт. Инкассаторы вставили задом наперед 
 11.12.2025 отремонтирована, готова к отправке</t>
   </si>
+  <si>
+    <t>10.11.2025 приехала в ремонт. Отремонтирована, ждет отправки</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -263,43 +274,46 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -308,7 +322,13 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -316,15 +336,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -5878,6 +5893,20 @@
         <v>32</v>
       </c>
     </row>
+    <row r="499" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A499" s="1">
+        <v>24905</v>
+      </c>
+      <c r="B499" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C499" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D499" s="24" t="s">
+        <v>33</v>
+      </c>
+    </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A505" s="1">
         <v>100297</v>

--- a/database.xlsx
+++ b/database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyServer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{511B6B25-0B1E-4864-AEA4-4768EE13BD51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{321BB9D2-12FD-43FD-B47F-5F54D39E9E1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="20910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="42">
   <si>
     <t>code</t>
   </si>
@@ -140,22 +140,60 @@
   </si>
   <si>
     <t>10.12.2025 приехала в ремонт. Инкассаторы вставили задом наперед 
-11.12.2025 отремонтирована, готова к отправке</t>
+11.12.2025 отремонтирована, готова к отправке
+11.12.2025 уехала клиенту</t>
   </si>
   <si>
-    <t>10.11.2025 приехала в ремонт. Отремонтирована, ждет отправки</t>
+    <t>10.11.2025 приехала в ремонт. Отремонтирована, ждет отправки
+11.11.2025 уехала клиенту</t>
+  </si>
+  <si>
+    <t>24.05.2026 приехала в ремонт ( вандалы забивали заблокированную сумку, разломаны детали механизма)
+26.05.2026  отремонтирована, готова к отправке</t>
+  </si>
+  <si>
+    <t>25.05.2026  Вставлялась задом наперед, видно по характерным следам. Порван мешок
+26.05.2026  отремонтирована, готова к отправке</t>
+  </si>
+  <si>
+    <t>30.04.2026 пришла в ремонт 
+1.05.2026 отремонтирована</t>
+  </si>
+  <si>
+    <t>31.03.2026 пришла в ремонт
+1.04.2026 отремонтирована (Заменено: фартук,  мешок, металлические уголки)</t>
+  </si>
+  <si>
+    <t>22617К</t>
+  </si>
+  <si>
+    <t>23013S</t>
+  </si>
+  <si>
+    <t>23011S</t>
+  </si>
+  <si>
+    <t>19.11.2025 уехала из ремонта</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -274,43 +312,46 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -319,27 +360,38 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -623,7 +675,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D1170"/>
+  <dimension ref="A1:D1267"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" style="1" customWidth="1"/>
@@ -782,12 +834,15 @@
         <v>45412</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>24792</v>
       </c>
       <c r="C12" s="8">
         <v>45397</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -5879,7 +5934,7 @@
         <v>45616</v>
       </c>
     </row>
-    <row r="498" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A498" s="1">
         <v>24969</v>
       </c>
@@ -5889,3351 +5944,4215 @@
       <c r="C498" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="D498" s="22" t="s">
+      <c r="D498" s="23" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="499" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A499" s="1">
         <v>24905</v>
       </c>
-      <c r="B499" s="23" t="s">
+      <c r="B499" s="22" t="s">
         <v>19</v>
       </c>
       <c r="C499" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="D499" s="24" t="s">
+      <c r="D499" s="23" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="500" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A500" s="1">
+        <v>25760</v>
+      </c>
+      <c r="B500" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C500" s="8">
+        <v>46169</v>
+      </c>
+    </row>
+    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A501" s="1">
+        <v>25759</v>
+      </c>
+      <c r="B501" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C501" s="8">
+        <v>46169</v>
+      </c>
+    </row>
+    <row r="502" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A502" s="1">
+        <v>25758</v>
+      </c>
+      <c r="B502" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C502" s="8">
+        <v>46169</v>
+      </c>
+    </row>
+    <row r="503" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A503" s="1">
+        <v>25757</v>
+      </c>
+      <c r="B503" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C503" s="8">
+        <v>46169</v>
+      </c>
+    </row>
+    <row r="504" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A504" s="1">
+        <v>25756</v>
+      </c>
+      <c r="B504" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C504" s="8">
+        <v>46169</v>
       </c>
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A505" s="1">
-        <v>100297</v>
+        <v>25755</v>
+      </c>
+      <c r="B505" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C505" s="8">
+        <v>46169</v>
       </c>
     </row>
     <row r="506" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A506" s="1">
-        <v>100298</v>
+        <v>25699</v>
+      </c>
+      <c r="B506" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C506" s="8">
+        <v>46169</v>
       </c>
     </row>
     <row r="507" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A507" s="1">
-        <v>100299</v>
+        <v>25698</v>
+      </c>
+      <c r="B507" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C507" s="8">
+        <v>46169</v>
       </c>
     </row>
     <row r="508" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A508" s="1">
-        <v>100300</v>
+        <v>25700</v>
+      </c>
+      <c r="B508" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C508" s="8">
+        <v>46169</v>
       </c>
     </row>
     <row r="509" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A509" s="1">
-        <v>100301</v>
-      </c>
-    </row>
-    <row r="510" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A510" s="1">
-        <v>100302</v>
-      </c>
-    </row>
-    <row r="511" spans="1:4" x14ac:dyDescent="0.25">
+        <v>25754</v>
+      </c>
+      <c r="B509" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C509" s="8">
+        <v>46169</v>
+      </c>
+    </row>
+    <row r="510" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A510" s="24">
+        <v>24959</v>
+      </c>
+      <c r="B510" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C510" s="8">
+        <v>46169</v>
+      </c>
+      <c r="D510" s="23" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="511" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A511" s="1">
-        <v>100303</v>
+        <v>24964</v>
+      </c>
+      <c r="B511" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C511" s="8">
+        <v>46169</v>
+      </c>
+      <c r="D511" s="23" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="512" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A512" s="1">
-        <v>100304</v>
-      </c>
-    </row>
-    <row r="513" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25752</v>
+      </c>
+      <c r="B512" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C512" s="8">
+        <v>46157</v>
+      </c>
+    </row>
+    <row r="513" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A513" s="1">
-        <v>100305</v>
-      </c>
-    </row>
-    <row r="514" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25753</v>
+      </c>
+      <c r="B513" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C513" s="8">
+        <v>46157</v>
+      </c>
+    </row>
+    <row r="514" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A514" s="1">
-        <v>100306</v>
-      </c>
-    </row>
-    <row r="515" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A515" s="1">
-        <v>100307</v>
-      </c>
-    </row>
-    <row r="516" spans="1:1" x14ac:dyDescent="0.25">
+        <v>24805</v>
+      </c>
+      <c r="D514" s="23" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="515" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A515" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="D515" s="23" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A516" s="1">
-        <v>100308</v>
-      </c>
-    </row>
-    <row r="517" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25702</v>
+      </c>
+      <c r="B516" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C516" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="517" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A517" s="1">
-        <v>100309</v>
-      </c>
-    </row>
-    <row r="518" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25703</v>
+      </c>
+      <c r="B517" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C517" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="518" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A518" s="1">
-        <v>100310</v>
-      </c>
-    </row>
-    <row r="519" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25704</v>
+      </c>
+      <c r="B518" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C518" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="519" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A519" s="1">
-        <v>100311</v>
-      </c>
-    </row>
-    <row r="520" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25705</v>
+      </c>
+      <c r="B519" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C519" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="520" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A520" s="1">
-        <v>100312</v>
-      </c>
-    </row>
-    <row r="521" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25706</v>
+      </c>
+      <c r="B520" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C520" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="521" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A521" s="1">
-        <v>100313</v>
-      </c>
-    </row>
-    <row r="522" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25707</v>
+      </c>
+      <c r="B521" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C521" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="522" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A522" s="1">
-        <v>100314</v>
-      </c>
-    </row>
-    <row r="523" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25708</v>
+      </c>
+      <c r="B522" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C522" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="523" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A523" s="1">
-        <v>100315</v>
-      </c>
-    </row>
-    <row r="524" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25709</v>
+      </c>
+      <c r="B523" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C523" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="524" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A524" s="1">
-        <v>100316</v>
-      </c>
-    </row>
-    <row r="525" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25710</v>
+      </c>
+      <c r="B524" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C524" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="525" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A525" s="1">
-        <v>100317</v>
-      </c>
-    </row>
-    <row r="526" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25711</v>
+      </c>
+      <c r="B525" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C525" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="526" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A526" s="1">
-        <v>100318</v>
-      </c>
-    </row>
-    <row r="527" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25712</v>
+      </c>
+      <c r="B526" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C526" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="527" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A527" s="1">
-        <v>100319</v>
-      </c>
-    </row>
-    <row r="528" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25713</v>
+      </c>
+      <c r="B527" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C527" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="528" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A528" s="1">
-        <v>100320</v>
-      </c>
-    </row>
-    <row r="529" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25714</v>
+      </c>
+      <c r="B528" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C528" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="529" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A529" s="1">
-        <v>100321</v>
-      </c>
-    </row>
-    <row r="530" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25715</v>
+      </c>
+      <c r="B529" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C529" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="530" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A530" s="1">
-        <v>100322</v>
-      </c>
-    </row>
-    <row r="531" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25716</v>
+      </c>
+      <c r="B530" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C530" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="531" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A531" s="1">
-        <v>100323</v>
-      </c>
-    </row>
-    <row r="532" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25717</v>
+      </c>
+      <c r="B531" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C531" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="532" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A532" s="1">
-        <v>100324</v>
-      </c>
-    </row>
-    <row r="533" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25718</v>
+      </c>
+      <c r="B532" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C532" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="533" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A533" s="1">
-        <v>100325</v>
-      </c>
-    </row>
-    <row r="534" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25719</v>
+      </c>
+      <c r="B533" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C533" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="534" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A534" s="1">
-        <v>100326</v>
-      </c>
-    </row>
-    <row r="535" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25720</v>
+      </c>
+      <c r="B534" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C534" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="535" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A535" s="1">
-        <v>100327</v>
-      </c>
-    </row>
-    <row r="536" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25721</v>
+      </c>
+      <c r="B535" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C535" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="536" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A536" s="1">
-        <v>100328</v>
-      </c>
-    </row>
-    <row r="537" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25722</v>
+      </c>
+      <c r="B536" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C536" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="537" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A537" s="1">
-        <v>100329</v>
-      </c>
-    </row>
-    <row r="538" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25723</v>
+      </c>
+      <c r="B537" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C537" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="538" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A538" s="1">
-        <v>100330</v>
-      </c>
-    </row>
-    <row r="539" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25724</v>
+      </c>
+      <c r="B538" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C538" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="539" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A539" s="1">
-        <v>100331</v>
-      </c>
-    </row>
-    <row r="540" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25725</v>
+      </c>
+      <c r="B539" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C539" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="540" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A540" s="1">
-        <v>100332</v>
-      </c>
-    </row>
-    <row r="541" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25726</v>
+      </c>
+      <c r="B540" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C540" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="541" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A541" s="1">
-        <v>100333</v>
-      </c>
-    </row>
-    <row r="542" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25727</v>
+      </c>
+      <c r="B541" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C541" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="542" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A542" s="1">
-        <v>100334</v>
-      </c>
-    </row>
-    <row r="543" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25728</v>
+      </c>
+      <c r="B542" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C542" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="543" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A543" s="1">
-        <v>100335</v>
-      </c>
-    </row>
-    <row r="544" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25729</v>
+      </c>
+      <c r="B543" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C543" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="544" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A544" s="1">
-        <v>100336</v>
-      </c>
-    </row>
-    <row r="545" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25730</v>
+      </c>
+      <c r="B544" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C544" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="545" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A545" s="1">
-        <v>100337</v>
-      </c>
-    </row>
-    <row r="546" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25731</v>
+      </c>
+      <c r="B545" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C545" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="546" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A546" s="1">
-        <v>100338</v>
-      </c>
-    </row>
-    <row r="547" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25732</v>
+      </c>
+      <c r="B546" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C546" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="547" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A547" s="1">
-        <v>100339</v>
-      </c>
-    </row>
-    <row r="548" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25733</v>
+      </c>
+      <c r="B547" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C547" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="548" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A548" s="1">
-        <v>100340</v>
-      </c>
-    </row>
-    <row r="549" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25734</v>
+      </c>
+      <c r="B548" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C548" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="549" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A549" s="1">
-        <v>100341</v>
-      </c>
-    </row>
-    <row r="550" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25735</v>
+      </c>
+      <c r="B549" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C549" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="550" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A550" s="1">
-        <v>100342</v>
-      </c>
-    </row>
-    <row r="551" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25736</v>
+      </c>
+      <c r="B550" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C550" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="551" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A551" s="1">
-        <v>100343</v>
-      </c>
-    </row>
-    <row r="552" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25737</v>
+      </c>
+      <c r="B551" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C551" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="552" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A552" s="1">
-        <v>100344</v>
-      </c>
-    </row>
-    <row r="553" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25738</v>
+      </c>
+      <c r="B552" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C552" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="553" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A553" s="1">
-        <v>100345</v>
-      </c>
-    </row>
-    <row r="554" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25739</v>
+      </c>
+      <c r="B553" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C553" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="554" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A554" s="1">
-        <v>100346</v>
-      </c>
-    </row>
-    <row r="555" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25740</v>
+      </c>
+      <c r="B554" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C554" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="555" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A555" s="1">
-        <v>100347</v>
-      </c>
-    </row>
-    <row r="556" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25741</v>
+      </c>
+      <c r="B555" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C555" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="556" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A556" s="1">
-        <v>100348</v>
-      </c>
-    </row>
-    <row r="557" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25742</v>
+      </c>
+      <c r="B556" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C556" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="557" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A557" s="1">
-        <v>100349</v>
-      </c>
-    </row>
-    <row r="558" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25743</v>
+      </c>
+      <c r="B557" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C557" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="558" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A558" s="1">
-        <v>100350</v>
-      </c>
-    </row>
-    <row r="559" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25744</v>
+      </c>
+      <c r="B558" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C558" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="559" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A559" s="1">
-        <v>100351</v>
-      </c>
-    </row>
-    <row r="560" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25745</v>
+      </c>
+      <c r="B559" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C559" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="560" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A560" s="1">
-        <v>100352</v>
-      </c>
-    </row>
-    <row r="561" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25746</v>
+      </c>
+      <c r="B560" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C560" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="561" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A561" s="1">
-        <v>100353</v>
-      </c>
-    </row>
-    <row r="562" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25747</v>
+      </c>
+      <c r="B561" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C561" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="562" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A562" s="1">
-        <v>100354</v>
-      </c>
-    </row>
-    <row r="563" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25748</v>
+      </c>
+      <c r="B562" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C562" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="563" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A563" s="1">
-        <v>100355</v>
-      </c>
-    </row>
-    <row r="564" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25749</v>
+      </c>
+      <c r="B563" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C563" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="564" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A564" s="1">
-        <v>100356</v>
-      </c>
-    </row>
-    <row r="565" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25750</v>
+      </c>
+      <c r="B564" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C564" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="565" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A565" s="1">
-        <v>100357</v>
-      </c>
-    </row>
-    <row r="566" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25751</v>
+      </c>
+      <c r="B565" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C565" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="566" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A566" s="1">
-        <v>100358</v>
-      </c>
-    </row>
-    <row r="567" spans="1:1" x14ac:dyDescent="0.25">
+        <v>26571</v>
+      </c>
+      <c r="B566" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C566" s="27">
+        <v>46090</v>
+      </c>
+    </row>
+    <row r="567" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A567" s="1">
-        <v>100359</v>
-      </c>
-    </row>
-    <row r="568" spans="1:1" x14ac:dyDescent="0.25">
+        <v>26572</v>
+      </c>
+      <c r="B567" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C567" s="27">
+        <v>46090</v>
+      </c>
+    </row>
+    <row r="568" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A568" s="1">
-        <v>100360</v>
-      </c>
-    </row>
-    <row r="569" spans="1:1" x14ac:dyDescent="0.25">
+        <v>26573</v>
+      </c>
+      <c r="B568" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C568" s="27">
+        <v>46090</v>
+      </c>
+    </row>
+    <row r="569" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A569" s="1">
-        <v>100361</v>
-      </c>
-    </row>
-    <row r="570" spans="1:1" x14ac:dyDescent="0.25">
+        <v>26574</v>
+      </c>
+      <c r="B569" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C569" s="27">
+        <v>46090</v>
+      </c>
+    </row>
+    <row r="570" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A570" s="1">
-        <v>100362</v>
-      </c>
-    </row>
-    <row r="571" spans="1:1" x14ac:dyDescent="0.25">
+        <v>26575</v>
+      </c>
+      <c r="B570" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C570" s="27">
+        <v>46090</v>
+      </c>
+    </row>
+    <row r="571" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A571" s="1">
-        <v>100363</v>
-      </c>
-    </row>
-    <row r="572" spans="1:1" x14ac:dyDescent="0.25">
+        <v>26576</v>
+      </c>
+      <c r="B571" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C571" s="27">
+        <v>46090</v>
+      </c>
+    </row>
+    <row r="572" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A572" s="1">
-        <v>100364</v>
-      </c>
-    </row>
-    <row r="573" spans="1:1" x14ac:dyDescent="0.25">
+        <v>26577</v>
+      </c>
+      <c r="B572" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C572" s="27">
+        <v>46090</v>
+      </c>
+    </row>
+    <row r="573" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A573" s="1">
-        <v>100365</v>
-      </c>
-    </row>
-    <row r="574" spans="1:1" x14ac:dyDescent="0.25">
+        <v>26578</v>
+      </c>
+      <c r="B573" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C573" s="27">
+        <v>46090</v>
+      </c>
+    </row>
+    <row r="574" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A574" s="1">
-        <v>100366</v>
-      </c>
-    </row>
-    <row r="575" spans="1:1" x14ac:dyDescent="0.25">
+        <v>26579</v>
+      </c>
+      <c r="B574" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C574" s="27">
+        <v>46090</v>
+      </c>
+    </row>
+    <row r="575" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A575" s="1">
-        <v>100367</v>
-      </c>
-    </row>
-    <row r="576" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A576" s="1">
-        <v>100368</v>
-      </c>
-    </row>
-    <row r="577" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A577" s="1">
-        <v>100369</v>
-      </c>
-    </row>
-    <row r="578" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A578" s="1">
-        <v>100370</v>
-      </c>
-    </row>
-    <row r="579" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A579" s="1">
-        <v>100371</v>
-      </c>
-    </row>
-    <row r="580" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A580" s="1">
-        <v>100372</v>
-      </c>
-    </row>
-    <row r="581" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A581" s="1">
-        <v>100373</v>
-      </c>
-    </row>
-    <row r="582" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A582" s="1">
-        <v>100374</v>
-      </c>
-    </row>
-    <row r="583" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A583" s="1">
-        <v>100375</v>
-      </c>
-    </row>
-    <row r="584" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A584" s="1">
-        <v>100376</v>
-      </c>
-    </row>
-    <row r="585" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A585" s="1">
-        <v>100377</v>
-      </c>
-    </row>
-    <row r="586" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A586" s="1">
-        <v>100378</v>
-      </c>
-    </row>
-    <row r="587" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A587" s="1">
-        <v>100379</v>
-      </c>
-    </row>
-    <row r="588" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A588" s="1">
-        <v>100380</v>
-      </c>
-    </row>
-    <row r="589" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A589" s="1">
-        <v>100381</v>
-      </c>
-    </row>
-    <row r="590" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A590" s="1">
-        <v>100382</v>
-      </c>
-    </row>
-    <row r="591" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A591" s="1">
-        <v>100383</v>
-      </c>
-    </row>
-    <row r="592" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A592" s="1">
-        <v>100384</v>
-      </c>
-    </row>
-    <row r="593" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A593" s="1">
-        <v>100385</v>
-      </c>
-    </row>
-    <row r="594" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A594" s="1">
-        <v>100386</v>
-      </c>
-    </row>
-    <row r="595" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A595" s="1">
-        <v>100387</v>
-      </c>
-    </row>
-    <row r="596" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A596" s="1">
-        <v>100388</v>
-      </c>
-    </row>
-    <row r="597" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A597" s="1">
-        <v>100389</v>
-      </c>
-    </row>
-    <row r="598" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A598" s="1">
-        <v>100390</v>
-      </c>
-    </row>
-    <row r="599" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A599" s="1">
-        <v>100391</v>
-      </c>
-    </row>
-    <row r="600" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A600" s="1">
-        <v>100392</v>
-      </c>
-    </row>
-    <row r="601" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A601" s="1">
-        <v>100393</v>
+        <v>26580</v>
+      </c>
+      <c r="B575" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C575" s="27">
+        <v>46090</v>
+      </c>
+    </row>
+    <row r="576" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A576" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="B576" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C576" s="8">
+        <v>45980</v>
+      </c>
+      <c r="D576" s="28" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="577" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A577" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B577" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C577" s="8">
+        <v>45980</v>
+      </c>
+      <c r="D577" s="28" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="602" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A602" s="1">
-        <v>100394</v>
+        <v>100297</v>
       </c>
     </row>
     <row r="603" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A603" s="1">
-        <v>100395</v>
+        <v>100298</v>
       </c>
     </row>
     <row r="604" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A604" s="1">
-        <v>100396</v>
+        <v>100299</v>
       </c>
     </row>
     <row r="605" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A605" s="1">
-        <v>100397</v>
+        <v>100300</v>
       </c>
     </row>
     <row r="606" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A606" s="1">
-        <v>100398</v>
+        <v>100301</v>
       </c>
     </row>
     <row r="607" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A607" s="1">
-        <v>100399</v>
+        <v>100302</v>
       </c>
     </row>
     <row r="608" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A608" s="1">
-        <v>100400</v>
+        <v>100303</v>
       </c>
     </row>
     <row r="609" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A609" s="1">
-        <v>100401</v>
+        <v>100304</v>
       </c>
     </row>
     <row r="610" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A610" s="1">
-        <v>100402</v>
+        <v>100305</v>
       </c>
     </row>
     <row r="611" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A611" s="1">
-        <v>100403</v>
+        <v>100306</v>
       </c>
     </row>
     <row r="612" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A612" s="1">
-        <v>100404</v>
+        <v>100307</v>
       </c>
     </row>
     <row r="613" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A613" s="1">
-        <v>100405</v>
+        <v>100308</v>
       </c>
     </row>
     <row r="614" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A614" s="1">
-        <v>100406</v>
+        <v>100309</v>
       </c>
     </row>
     <row r="615" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A615" s="1">
-        <v>100407</v>
+        <v>100310</v>
       </c>
     </row>
     <row r="616" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A616" s="1">
-        <v>100408</v>
+        <v>100311</v>
       </c>
     </row>
     <row r="617" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A617" s="1">
-        <v>100409</v>
+        <v>100312</v>
       </c>
     </row>
     <row r="618" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A618" s="1">
-        <v>100410</v>
+        <v>100313</v>
       </c>
     </row>
     <row r="619" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A619" s="1">
-        <v>100411</v>
+        <v>100314</v>
       </c>
     </row>
     <row r="620" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A620" s="1">
-        <v>100412</v>
+        <v>100315</v>
       </c>
     </row>
     <row r="621" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A621" s="1">
-        <v>100413</v>
+        <v>100316</v>
       </c>
     </row>
     <row r="622" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A622" s="1">
-        <v>100414</v>
+        <v>100317</v>
       </c>
     </row>
     <row r="623" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A623" s="1">
-        <v>100415</v>
+        <v>100318</v>
       </c>
     </row>
     <row r="624" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A624" s="1">
-        <v>100416</v>
+        <v>100319</v>
       </c>
     </row>
     <row r="625" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A625" s="1">
-        <v>100417</v>
+        <v>100320</v>
       </c>
     </row>
     <row r="626" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A626" s="1">
-        <v>100418</v>
+        <v>100321</v>
       </c>
     </row>
     <row r="627" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A627" s="1">
-        <v>100419</v>
+        <v>100322</v>
       </c>
     </row>
     <row r="628" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A628" s="1">
-        <v>100420</v>
+        <v>100323</v>
       </c>
     </row>
     <row r="629" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A629" s="1">
-        <v>100421</v>
+        <v>100324</v>
       </c>
     </row>
     <row r="630" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A630" s="1">
-        <v>100422</v>
+        <v>100325</v>
       </c>
     </row>
     <row r="631" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A631" s="1">
-        <v>100423</v>
+        <v>100326</v>
       </c>
     </row>
     <row r="632" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A632" s="1">
-        <v>100424</v>
+        <v>100327</v>
       </c>
     </row>
     <row r="633" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A633" s="1">
-        <v>100425</v>
+        <v>100328</v>
       </c>
     </row>
     <row r="634" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A634" s="1">
-        <v>100426</v>
+        <v>100329</v>
       </c>
     </row>
     <row r="635" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A635" s="1">
-        <v>100427</v>
+        <v>100330</v>
       </c>
     </row>
     <row r="636" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A636" s="1">
-        <v>100428</v>
+        <v>100331</v>
       </c>
     </row>
     <row r="637" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A637" s="1">
-        <v>100429</v>
+        <v>100332</v>
       </c>
     </row>
     <row r="638" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A638" s="1">
-        <v>100430</v>
+        <v>100333</v>
       </c>
     </row>
     <row r="639" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A639" s="1">
-        <v>100431</v>
+        <v>100334</v>
       </c>
     </row>
     <row r="640" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A640" s="1">
-        <v>100432</v>
+        <v>100335</v>
       </c>
     </row>
     <row r="641" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A641" s="1">
-        <v>100433</v>
+        <v>100336</v>
       </c>
     </row>
     <row r="642" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A642" s="1">
-        <v>100434</v>
+        <v>100337</v>
       </c>
     </row>
     <row r="643" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A643" s="1">
-        <v>100435</v>
+        <v>100338</v>
       </c>
     </row>
     <row r="644" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A644" s="1">
-        <v>100436</v>
+        <v>100339</v>
       </c>
     </row>
     <row r="645" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A645" s="1">
-        <v>100437</v>
+        <v>100340</v>
       </c>
     </row>
     <row r="646" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A646" s="1">
-        <v>100438</v>
+        <v>100341</v>
       </c>
     </row>
     <row r="647" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A647" s="1">
-        <v>100439</v>
+        <v>100342</v>
       </c>
     </row>
     <row r="648" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A648" s="1">
-        <v>100440</v>
+        <v>100343</v>
       </c>
     </row>
     <row r="649" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A649" s="1">
-        <v>100441</v>
+        <v>100344</v>
       </c>
     </row>
     <row r="650" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A650" s="1">
-        <v>100442</v>
+        <v>100345</v>
       </c>
     </row>
     <row r="651" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A651" s="1">
-        <v>100443</v>
+        <v>100346</v>
       </c>
     </row>
     <row r="652" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A652" s="1">
-        <v>100444</v>
+        <v>100347</v>
       </c>
     </row>
     <row r="653" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A653" s="1">
-        <v>100445</v>
+        <v>100348</v>
       </c>
     </row>
     <row r="654" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A654" s="1">
-        <v>100446</v>
+        <v>100349</v>
       </c>
     </row>
     <row r="655" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A655" s="1">
-        <v>100447</v>
+        <v>100350</v>
       </c>
     </row>
     <row r="656" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A656" s="1">
-        <v>100448</v>
+        <v>100351</v>
       </c>
     </row>
     <row r="657" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A657" s="1">
-        <v>100449</v>
+        <v>100352</v>
       </c>
     </row>
     <row r="658" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A658" s="1">
-        <v>100450</v>
+        <v>100353</v>
       </c>
     </row>
     <row r="659" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A659" s="1">
-        <v>100451</v>
+        <v>100354</v>
       </c>
     </row>
     <row r="660" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A660" s="1">
-        <v>100452</v>
+        <v>100355</v>
       </c>
     </row>
     <row r="661" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A661" s="1">
-        <v>100453</v>
+        <v>100356</v>
       </c>
     </row>
     <row r="662" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A662" s="1">
-        <v>100454</v>
+        <v>100357</v>
       </c>
     </row>
     <row r="663" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A663" s="1">
-        <v>100455</v>
+        <v>100358</v>
       </c>
     </row>
     <row r="664" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A664" s="1">
-        <v>100456</v>
+        <v>100359</v>
       </c>
     </row>
     <row r="665" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A665" s="1">
-        <v>100457</v>
+        <v>100360</v>
       </c>
     </row>
     <row r="666" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A666" s="1">
-        <v>100458</v>
+        <v>100361</v>
       </c>
     </row>
     <row r="667" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A667" s="1">
-        <v>100459</v>
+        <v>100362</v>
       </c>
     </row>
     <row r="668" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A668" s="1">
-        <v>100460</v>
+        <v>100363</v>
       </c>
     </row>
     <row r="669" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A669" s="1">
-        <v>100461</v>
+        <v>100364</v>
       </c>
     </row>
     <row r="670" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A670" s="1">
-        <v>100462</v>
+        <v>100365</v>
       </c>
     </row>
     <row r="671" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A671" s="1">
-        <v>100463</v>
+        <v>100366</v>
       </c>
     </row>
     <row r="672" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A672" s="1">
-        <v>100464</v>
+        <v>100367</v>
       </c>
     </row>
     <row r="673" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A673" s="1">
-        <v>100465</v>
+        <v>100368</v>
       </c>
     </row>
     <row r="674" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A674" s="1">
-        <v>100466</v>
+        <v>100369</v>
       </c>
     </row>
     <row r="675" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A675" s="1">
-        <v>100467</v>
+        <v>100370</v>
       </c>
     </row>
     <row r="676" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A676" s="1">
-        <v>100468</v>
+        <v>100371</v>
       </c>
     </row>
     <row r="677" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A677" s="1">
-        <v>100469</v>
+        <v>100372</v>
       </c>
     </row>
     <row r="678" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A678" s="1">
-        <v>100470</v>
+        <v>100373</v>
       </c>
     </row>
     <row r="679" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A679" s="1">
-        <v>100471</v>
+        <v>100374</v>
       </c>
     </row>
     <row r="680" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A680" s="1">
-        <v>100472</v>
+        <v>100375</v>
       </c>
     </row>
     <row r="681" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A681" s="1">
-        <v>100473</v>
+        <v>100376</v>
       </c>
     </row>
     <row r="682" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A682" s="1">
-        <v>100474</v>
+        <v>100377</v>
       </c>
     </row>
     <row r="683" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A683" s="1">
-        <v>100475</v>
+        <v>100378</v>
       </c>
     </row>
     <row r="684" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A684" s="1">
-        <v>100476</v>
+        <v>100379</v>
       </c>
     </row>
     <row r="685" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A685" s="1">
-        <v>100477</v>
+        <v>100380</v>
       </c>
     </row>
     <row r="686" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A686" s="1">
-        <v>100478</v>
+        <v>100381</v>
       </c>
     </row>
     <row r="687" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A687" s="1">
-        <v>100479</v>
+        <v>100382</v>
       </c>
     </row>
     <row r="688" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A688" s="1">
-        <v>100480</v>
+        <v>100383</v>
       </c>
     </row>
     <row r="689" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A689" s="1">
-        <v>100481</v>
+        <v>100384</v>
       </c>
     </row>
     <row r="690" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A690" s="1">
-        <v>100482</v>
+        <v>100385</v>
       </c>
     </row>
     <row r="691" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A691" s="1">
-        <v>100483</v>
+        <v>100386</v>
       </c>
     </row>
     <row r="692" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A692" s="1">
-        <v>100484</v>
+        <v>100387</v>
       </c>
     </row>
     <row r="693" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A693" s="1">
-        <v>100485</v>
+        <v>100388</v>
       </c>
     </row>
     <row r="694" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A694" s="1">
-        <v>100486</v>
+        <v>100389</v>
       </c>
     </row>
     <row r="695" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A695" s="1">
-        <v>100487</v>
+        <v>100390</v>
       </c>
     </row>
     <row r="696" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A696" s="1">
-        <v>100488</v>
+        <v>100391</v>
       </c>
     </row>
     <row r="697" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A697" s="1">
-        <v>100489</v>
+        <v>100392</v>
       </c>
     </row>
     <row r="698" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A698" s="1">
-        <v>100490</v>
+        <v>100393</v>
       </c>
     </row>
     <row r="699" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A699" s="1">
-        <v>100491</v>
+        <v>100394</v>
       </c>
     </row>
     <row r="700" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A700" s="1">
-        <v>100492</v>
+        <v>100395</v>
       </c>
     </row>
     <row r="701" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A701" s="1">
-        <v>100493</v>
+        <v>100396</v>
       </c>
     </row>
     <row r="702" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A702" s="1">
-        <v>100494</v>
+        <v>100397</v>
       </c>
     </row>
     <row r="703" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A703" s="1">
-        <v>100495</v>
+        <v>100398</v>
       </c>
     </row>
     <row r="704" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A704" s="1">
-        <v>100496</v>
+        <v>100399</v>
       </c>
     </row>
     <row r="705" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A705" s="1">
-        <v>100497</v>
+        <v>100400</v>
       </c>
     </row>
     <row r="706" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A706" s="1">
-        <v>100498</v>
+        <v>100401</v>
       </c>
     </row>
     <row r="707" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A707" s="1">
-        <v>100499</v>
+        <v>100402</v>
       </c>
     </row>
     <row r="708" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A708" s="1">
-        <v>100500</v>
+        <v>100403</v>
       </c>
     </row>
     <row r="709" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A709" s="1">
-        <v>100501</v>
+        <v>100404</v>
       </c>
     </row>
     <row r="710" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A710" s="1">
-        <v>100502</v>
+        <v>100405</v>
       </c>
     </row>
     <row r="711" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A711" s="1">
-        <v>100503</v>
+        <v>100406</v>
       </c>
     </row>
     <row r="712" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A712" s="1">
-        <v>100504</v>
+        <v>100407</v>
       </c>
     </row>
     <row r="713" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A713" s="1">
-        <v>100505</v>
+        <v>100408</v>
       </c>
     </row>
     <row r="714" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A714" s="1">
-        <v>100506</v>
+        <v>100409</v>
       </c>
     </row>
     <row r="715" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A715" s="1">
-        <v>100507</v>
+        <v>100410</v>
       </c>
     </row>
     <row r="716" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A716" s="1">
-        <v>100508</v>
+        <v>100411</v>
       </c>
     </row>
     <row r="717" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A717" s="1">
-        <v>100509</v>
+        <v>100412</v>
       </c>
     </row>
     <row r="718" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A718" s="1">
-        <v>100510</v>
+        <v>100413</v>
       </c>
     </row>
     <row r="719" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A719" s="1">
-        <v>100511</v>
+        <v>100414</v>
       </c>
     </row>
     <row r="720" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A720" s="1">
-        <v>100512</v>
+        <v>100415</v>
       </c>
     </row>
     <row r="721" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A721" s="1">
-        <v>100513</v>
+        <v>100416</v>
       </c>
     </row>
     <row r="722" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A722" s="1">
-        <v>100514</v>
+        <v>100417</v>
       </c>
     </row>
     <row r="723" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A723" s="1">
-        <v>100515</v>
+        <v>100418</v>
       </c>
     </row>
     <row r="724" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A724" s="1">
-        <v>100516</v>
+        <v>100419</v>
       </c>
     </row>
     <row r="725" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A725" s="1">
-        <v>100517</v>
+        <v>100420</v>
       </c>
     </row>
     <row r="726" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A726" s="1">
-        <v>100518</v>
+        <v>100421</v>
       </c>
     </row>
     <row r="727" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A727" s="1">
-        <v>100519</v>
+        <v>100422</v>
       </c>
     </row>
     <row r="728" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A728" s="1">
-        <v>100520</v>
+        <v>100423</v>
       </c>
     </row>
     <row r="729" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A729" s="1">
-        <v>100521</v>
+        <v>100424</v>
       </c>
     </row>
     <row r="730" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A730" s="1">
-        <v>100522</v>
+        <v>100425</v>
       </c>
     </row>
     <row r="731" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A731" s="1">
-        <v>100523</v>
+        <v>100426</v>
       </c>
     </row>
     <row r="732" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A732" s="1">
-        <v>100524</v>
+        <v>100427</v>
       </c>
     </row>
     <row r="733" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A733" s="1">
-        <v>100525</v>
+        <v>100428</v>
       </c>
     </row>
     <row r="734" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A734" s="1">
-        <v>100526</v>
+        <v>100429</v>
       </c>
     </row>
     <row r="735" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A735" s="1">
-        <v>100527</v>
+        <v>100430</v>
       </c>
     </row>
     <row r="736" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A736" s="1">
-        <v>100528</v>
+        <v>100431</v>
       </c>
     </row>
     <row r="737" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A737" s="1">
-        <v>100529</v>
+        <v>100432</v>
       </c>
     </row>
     <row r="738" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A738" s="1">
-        <v>100530</v>
+        <v>100433</v>
       </c>
     </row>
     <row r="739" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A739" s="1">
-        <v>100531</v>
+        <v>100434</v>
       </c>
     </row>
     <row r="740" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A740" s="1">
-        <v>100532</v>
+        <v>100435</v>
       </c>
     </row>
     <row r="741" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A741" s="1">
-        <v>100533</v>
+        <v>100436</v>
       </c>
     </row>
     <row r="742" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A742" s="1">
-        <v>100534</v>
+        <v>100437</v>
       </c>
     </row>
     <row r="743" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A743" s="1">
-        <v>100535</v>
+        <v>100438</v>
       </c>
     </row>
     <row r="744" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A744" s="1">
-        <v>100536</v>
+        <v>100439</v>
       </c>
     </row>
     <row r="745" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A745" s="1">
-        <v>100537</v>
+        <v>100440</v>
       </c>
     </row>
     <row r="746" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A746" s="1">
-        <v>100538</v>
+        <v>100441</v>
       </c>
     </row>
     <row r="747" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A747" s="1">
-        <v>100539</v>
+        <v>100442</v>
       </c>
     </row>
     <row r="748" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A748" s="1">
-        <v>100540</v>
+        <v>100443</v>
       </c>
     </row>
     <row r="749" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A749" s="1">
-        <v>100541</v>
+        <v>100444</v>
       </c>
     </row>
     <row r="750" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A750" s="1">
-        <v>100542</v>
+        <v>100445</v>
       </c>
     </row>
     <row r="751" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A751" s="1">
-        <v>100543</v>
+        <v>100446</v>
       </c>
     </row>
     <row r="752" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A752" s="1">
-        <v>100544</v>
+        <v>100447</v>
       </c>
     </row>
     <row r="753" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A753" s="1">
-        <v>100545</v>
+        <v>100448</v>
       </c>
     </row>
     <row r="754" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A754" s="1">
-        <v>100546</v>
+        <v>100449</v>
       </c>
     </row>
     <row r="755" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A755" s="1">
-        <v>100547</v>
+        <v>100450</v>
       </c>
     </row>
     <row r="756" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A756" s="1">
-        <v>100548</v>
+        <v>100451</v>
       </c>
     </row>
     <row r="757" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A757" s="1">
-        <v>100549</v>
+        <v>100452</v>
       </c>
     </row>
     <row r="758" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A758" s="1">
-        <v>100550</v>
+        <v>100453</v>
       </c>
     </row>
     <row r="759" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A759" s="1">
-        <v>100551</v>
+        <v>100454</v>
       </c>
     </row>
     <row r="760" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A760" s="1">
-        <v>100552</v>
+        <v>100455</v>
       </c>
     </row>
     <row r="761" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A761" s="1">
-        <v>100553</v>
+        <v>100456</v>
       </c>
     </row>
     <row r="762" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A762" s="1">
-        <v>100554</v>
+        <v>100457</v>
       </c>
     </row>
     <row r="763" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A763" s="1">
-        <v>100555</v>
+        <v>100458</v>
       </c>
     </row>
     <row r="764" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A764" s="1">
-        <v>100556</v>
+        <v>100459</v>
       </c>
     </row>
     <row r="765" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A765" s="1">
-        <v>100557</v>
+        <v>100460</v>
       </c>
     </row>
     <row r="766" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A766" s="1">
-        <v>100558</v>
+        <v>100461</v>
       </c>
     </row>
     <row r="767" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A767" s="1">
-        <v>100559</v>
+        <v>100462</v>
       </c>
     </row>
     <row r="768" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A768" s="1">
-        <v>100560</v>
+        <v>100463</v>
       </c>
     </row>
     <row r="769" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A769" s="1">
-        <v>100561</v>
+        <v>100464</v>
       </c>
     </row>
     <row r="770" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A770" s="1">
-        <v>100562</v>
+        <v>100465</v>
       </c>
     </row>
     <row r="771" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A771" s="1">
-        <v>100563</v>
+        <v>100466</v>
       </c>
     </row>
     <row r="772" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A772" s="1">
-        <v>100564</v>
+        <v>100467</v>
       </c>
     </row>
     <row r="773" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A773" s="1">
-        <v>100565</v>
+        <v>100468</v>
       </c>
     </row>
     <row r="774" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A774" s="1">
-        <v>100566</v>
+        <v>100469</v>
       </c>
     </row>
     <row r="775" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A775" s="1">
-        <v>100567</v>
+        <v>100470</v>
       </c>
     </row>
     <row r="776" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A776" s="1">
-        <v>100568</v>
+        <v>100471</v>
       </c>
     </row>
     <row r="777" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A777" s="1">
-        <v>100569</v>
+        <v>100472</v>
       </c>
     </row>
     <row r="778" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A778" s="1">
-        <v>100570</v>
+        <v>100473</v>
       </c>
     </row>
     <row r="779" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A779" s="1">
-        <v>100571</v>
+        <v>100474</v>
       </c>
     </row>
     <row r="780" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A780" s="1">
-        <v>100572</v>
+        <v>100475</v>
       </c>
     </row>
     <row r="781" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A781" s="1">
-        <v>100573</v>
+        <v>100476</v>
       </c>
     </row>
     <row r="782" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A782" s="1">
-        <v>100574</v>
+        <v>100477</v>
       </c>
     </row>
     <row r="783" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A783" s="1">
-        <v>100575</v>
+        <v>100478</v>
       </c>
     </row>
     <row r="784" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A784" s="1">
-        <v>100576</v>
+        <v>100479</v>
       </c>
     </row>
     <row r="785" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A785" s="1">
-        <v>100577</v>
+        <v>100480</v>
       </c>
     </row>
     <row r="786" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A786" s="1">
-        <v>100578</v>
+        <v>100481</v>
       </c>
     </row>
     <row r="787" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A787" s="1">
-        <v>100579</v>
+        <v>100482</v>
       </c>
     </row>
     <row r="788" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A788" s="1">
-        <v>100580</v>
+        <v>100483</v>
       </c>
     </row>
     <row r="789" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A789" s="1">
-        <v>100581</v>
+        <v>100484</v>
       </c>
     </row>
     <row r="790" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A790" s="1">
-        <v>100582</v>
+        <v>100485</v>
       </c>
     </row>
     <row r="791" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A791" s="1">
-        <v>100583</v>
+        <v>100486</v>
       </c>
     </row>
     <row r="792" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A792" s="1">
-        <v>100584</v>
+        <v>100487</v>
       </c>
     </row>
     <row r="793" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A793" s="1">
-        <v>100585</v>
+        <v>100488</v>
       </c>
     </row>
     <row r="794" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A794" s="1">
-        <v>100586</v>
+        <v>100489</v>
       </c>
     </row>
     <row r="795" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A795" s="1">
-        <v>100587</v>
+        <v>100490</v>
       </c>
     </row>
     <row r="796" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A796" s="1">
-        <v>100588</v>
+        <v>100491</v>
       </c>
     </row>
     <row r="797" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A797" s="1">
-        <v>100589</v>
+        <v>100492</v>
       </c>
     </row>
     <row r="798" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A798" s="1">
-        <v>100590</v>
+        <v>100493</v>
       </c>
     </row>
     <row r="799" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A799" s="1">
-        <v>100591</v>
+        <v>100494</v>
       </c>
     </row>
     <row r="800" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A800" s="1">
-        <v>100592</v>
+        <v>100495</v>
       </c>
     </row>
     <row r="801" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A801" s="1">
-        <v>100593</v>
+        <v>100496</v>
       </c>
     </row>
     <row r="802" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A802" s="1">
-        <v>100594</v>
+        <v>100497</v>
       </c>
     </row>
     <row r="803" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A803" s="1">
-        <v>100595</v>
+        <v>100498</v>
       </c>
     </row>
     <row r="804" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A804" s="1">
-        <v>100596</v>
+        <v>100499</v>
       </c>
     </row>
     <row r="805" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A805" s="1">
-        <v>100597</v>
+        <v>100500</v>
       </c>
     </row>
     <row r="806" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A806" s="1">
-        <v>100598</v>
+        <v>100501</v>
       </c>
     </row>
     <row r="807" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A807" s="1">
-        <v>100599</v>
+        <v>100502</v>
       </c>
     </row>
     <row r="808" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A808" s="1">
-        <v>100600</v>
+        <v>100503</v>
       </c>
     </row>
     <row r="809" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A809" s="1">
-        <v>100601</v>
+        <v>100504</v>
       </c>
     </row>
     <row r="810" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A810" s="1">
-        <v>100602</v>
+        <v>100505</v>
       </c>
     </row>
     <row r="811" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A811" s="1">
-        <v>100603</v>
+        <v>100506</v>
       </c>
     </row>
     <row r="812" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A812" s="1">
-        <v>100604</v>
+        <v>100507</v>
       </c>
     </row>
     <row r="813" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A813" s="1">
-        <v>100605</v>
+        <v>100508</v>
       </c>
     </row>
     <row r="814" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A814" s="1">
-        <v>100606</v>
+        <v>100509</v>
       </c>
     </row>
     <row r="815" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A815" s="1">
-        <v>100607</v>
+        <v>100510</v>
       </c>
     </row>
     <row r="816" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A816" s="1">
-        <v>100608</v>
+        <v>100511</v>
       </c>
     </row>
     <row r="817" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A817" s="1">
-        <v>100609</v>
+        <v>100512</v>
       </c>
     </row>
     <row r="818" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A818" s="1">
-        <v>100610</v>
+        <v>100513</v>
       </c>
     </row>
     <row r="819" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A819" s="1">
-        <v>100611</v>
+        <v>100514</v>
       </c>
     </row>
     <row r="820" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A820" s="1">
-        <v>100612</v>
+        <v>100515</v>
       </c>
     </row>
     <row r="821" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A821" s="1">
-        <v>100613</v>
+        <v>100516</v>
       </c>
     </row>
     <row r="822" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A822" s="1">
-        <v>100614</v>
+        <v>100517</v>
       </c>
     </row>
     <row r="823" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A823" s="1">
-        <v>100615</v>
+        <v>100518</v>
       </c>
     </row>
     <row r="824" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A824" s="1">
-        <v>100616</v>
+        <v>100519</v>
       </c>
     </row>
     <row r="825" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A825" s="1">
-        <v>100617</v>
+        <v>100520</v>
       </c>
     </row>
     <row r="826" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A826" s="1">
-        <v>100618</v>
+        <v>100521</v>
       </c>
     </row>
     <row r="827" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A827" s="1">
-        <v>100619</v>
+        <v>100522</v>
       </c>
     </row>
     <row r="828" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A828" s="1">
-        <v>100620</v>
+        <v>100523</v>
       </c>
     </row>
     <row r="829" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A829" s="1">
-        <v>100621</v>
+        <v>100524</v>
       </c>
     </row>
     <row r="830" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A830" s="1">
-        <v>100622</v>
+        <v>100525</v>
       </c>
     </row>
     <row r="831" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A831" s="1">
-        <v>100623</v>
+        <v>100526</v>
       </c>
     </row>
     <row r="832" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A832" s="1">
-        <v>100624</v>
+        <v>100527</v>
       </c>
     </row>
     <row r="833" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A833" s="1">
-        <v>100625</v>
+        <v>100528</v>
       </c>
     </row>
     <row r="834" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A834" s="1">
-        <v>100626</v>
+        <v>100529</v>
       </c>
     </row>
     <row r="835" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A835" s="1">
-        <v>100627</v>
+        <v>100530</v>
       </c>
     </row>
     <row r="836" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A836" s="1">
-        <v>100628</v>
+        <v>100531</v>
       </c>
     </row>
     <row r="837" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A837" s="1">
-        <v>100629</v>
+        <v>100532</v>
       </c>
     </row>
     <row r="838" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A838" s="1">
-        <v>100630</v>
+        <v>100533</v>
       </c>
     </row>
     <row r="839" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A839" s="1">
-        <v>100631</v>
+        <v>100534</v>
       </c>
     </row>
     <row r="840" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A840" s="1">
-        <v>100632</v>
+        <v>100535</v>
       </c>
     </row>
     <row r="841" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A841" s="1">
-        <v>100633</v>
+        <v>100536</v>
       </c>
     </row>
     <row r="842" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A842" s="1">
-        <v>100634</v>
+        <v>100537</v>
       </c>
     </row>
     <row r="843" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A843" s="1">
-        <v>100635</v>
+        <v>100538</v>
       </c>
     </row>
     <row r="844" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A844" s="1">
-        <v>100636</v>
+        <v>100539</v>
       </c>
     </row>
     <row r="845" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A845" s="1">
-        <v>100637</v>
+        <v>100540</v>
       </c>
     </row>
     <row r="846" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A846" s="1">
-        <v>100638</v>
+        <v>100541</v>
       </c>
     </row>
     <row r="847" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A847" s="1">
-        <v>100639</v>
+        <v>100542</v>
       </c>
     </row>
     <row r="848" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A848" s="1">
-        <v>100640</v>
+        <v>100543</v>
       </c>
     </row>
     <row r="849" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A849" s="1">
-        <v>100641</v>
+        <v>100544</v>
       </c>
     </row>
     <row r="850" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A850" s="1">
-        <v>100642</v>
+        <v>100545</v>
       </c>
     </row>
     <row r="851" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A851" s="1">
-        <v>100643</v>
+        <v>100546</v>
       </c>
     </row>
     <row r="852" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A852" s="1">
-        <v>100644</v>
+        <v>100547</v>
       </c>
     </row>
     <row r="853" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A853" s="1">
-        <v>100645</v>
+        <v>100548</v>
       </c>
     </row>
     <row r="854" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A854" s="1">
-        <v>100646</v>
+        <v>100549</v>
       </c>
     </row>
     <row r="855" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A855" s="1">
-        <v>100647</v>
+        <v>100550</v>
       </c>
     </row>
     <row r="856" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A856" s="1">
-        <v>100648</v>
+        <v>100551</v>
       </c>
     </row>
     <row r="857" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A857" s="1">
-        <v>100649</v>
+        <v>100552</v>
       </c>
     </row>
     <row r="858" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A858" s="1">
-        <v>100650</v>
+        <v>100553</v>
       </c>
     </row>
     <row r="859" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A859" s="1">
-        <v>100651</v>
+        <v>100554</v>
       </c>
     </row>
     <row r="860" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A860" s="1">
-        <v>100652</v>
+        <v>100555</v>
       </c>
     </row>
     <row r="861" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A861" s="1">
-        <v>100653</v>
+        <v>100556</v>
       </c>
     </row>
     <row r="862" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A862" s="1">
-        <v>100654</v>
+        <v>100557</v>
       </c>
     </row>
     <row r="863" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A863" s="1">
-        <v>100655</v>
+        <v>100558</v>
       </c>
     </row>
     <row r="864" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A864" s="1">
-        <v>100656</v>
+        <v>100559</v>
       </c>
     </row>
     <row r="865" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A865" s="1">
-        <v>100657</v>
+        <v>100560</v>
       </c>
     </row>
     <row r="866" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A866" s="1">
-        <v>100658</v>
+        <v>100561</v>
       </c>
     </row>
     <row r="867" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A867" s="1">
-        <v>100659</v>
+        <v>100562</v>
       </c>
     </row>
     <row r="868" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A868" s="1">
-        <v>100660</v>
+        <v>100563</v>
       </c>
     </row>
     <row r="869" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A869" s="1">
-        <v>100661</v>
+        <v>100564</v>
       </c>
     </row>
     <row r="870" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A870" s="1">
-        <v>100662</v>
+        <v>100565</v>
       </c>
     </row>
     <row r="871" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A871" s="1">
-        <v>100663</v>
+        <v>100566</v>
       </c>
     </row>
     <row r="872" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A872" s="1">
-        <v>100664</v>
+        <v>100567</v>
       </c>
     </row>
     <row r="873" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A873" s="1">
-        <v>100665</v>
+        <v>100568</v>
       </c>
     </row>
     <row r="874" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A874" s="1">
-        <v>100666</v>
+        <v>100569</v>
       </c>
     </row>
     <row r="875" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A875" s="1">
-        <v>100667</v>
+        <v>100570</v>
       </c>
     </row>
     <row r="876" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A876" s="1">
-        <v>100668</v>
+        <v>100571</v>
       </c>
     </row>
     <row r="877" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A877" s="1">
-        <v>100669</v>
+        <v>100572</v>
       </c>
     </row>
     <row r="878" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A878" s="1">
-        <v>100670</v>
+        <v>100573</v>
       </c>
     </row>
     <row r="879" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A879" s="1">
-        <v>100671</v>
+        <v>100574</v>
       </c>
     </row>
     <row r="880" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A880" s="1">
-        <v>100672</v>
+        <v>100575</v>
       </c>
     </row>
     <row r="881" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A881" s="1">
-        <v>100673</v>
+        <v>100576</v>
       </c>
     </row>
     <row r="882" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A882" s="1">
-        <v>100674</v>
+        <v>100577</v>
       </c>
     </row>
     <row r="883" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A883" s="1">
-        <v>100675</v>
+        <v>100578</v>
       </c>
     </row>
     <row r="884" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A884" s="1">
-        <v>100676</v>
+        <v>100579</v>
       </c>
     </row>
     <row r="885" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A885" s="1">
-        <v>100677</v>
+        <v>100580</v>
       </c>
     </row>
     <row r="886" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A886" s="1">
-        <v>100678</v>
+        <v>100581</v>
       </c>
     </row>
     <row r="887" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A887" s="1">
-        <v>100679</v>
+        <v>100582</v>
       </c>
     </row>
     <row r="888" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A888" s="1">
-        <v>100680</v>
+        <v>100583</v>
       </c>
     </row>
     <row r="889" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A889" s="1">
-        <v>100681</v>
+        <v>100584</v>
       </c>
     </row>
     <row r="890" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A890" s="1">
-        <v>100682</v>
+        <v>100585</v>
       </c>
     </row>
     <row r="891" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A891" s="1">
-        <v>100683</v>
+        <v>100586</v>
       </c>
     </row>
     <row r="892" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A892" s="1">
-        <v>100684</v>
+        <v>100587</v>
       </c>
     </row>
     <row r="893" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A893" s="1">
-        <v>100685</v>
+        <v>100588</v>
       </c>
     </row>
     <row r="894" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A894" s="1">
-        <v>100686</v>
+        <v>100589</v>
       </c>
     </row>
     <row r="895" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A895" s="1">
-        <v>100687</v>
+        <v>100590</v>
       </c>
     </row>
     <row r="896" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A896" s="1">
-        <v>100688</v>
+        <v>100591</v>
       </c>
     </row>
     <row r="897" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A897" s="1">
-        <v>100689</v>
+        <v>100592</v>
       </c>
     </row>
     <row r="898" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A898" s="1">
-        <v>100690</v>
+        <v>100593</v>
       </c>
     </row>
     <row r="899" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A899" s="1">
-        <v>100691</v>
+        <v>100594</v>
       </c>
     </row>
     <row r="900" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A900" s="1">
-        <v>100692</v>
+        <v>100595</v>
       </c>
     </row>
     <row r="901" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A901" s="1">
-        <v>100693</v>
+        <v>100596</v>
       </c>
     </row>
     <row r="902" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A902" s="1">
-        <v>100694</v>
+        <v>100597</v>
       </c>
     </row>
     <row r="903" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A903" s="1">
-        <v>100695</v>
+        <v>100598</v>
       </c>
     </row>
     <row r="904" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A904" s="1">
-        <v>100696</v>
+        <v>100599</v>
       </c>
     </row>
     <row r="905" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A905" s="1">
-        <v>100697</v>
+        <v>100600</v>
       </c>
     </row>
     <row r="906" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A906" s="1">
-        <v>100698</v>
+        <v>100601</v>
       </c>
     </row>
     <row r="907" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A907" s="1">
-        <v>100699</v>
+        <v>100602</v>
       </c>
     </row>
     <row r="908" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A908" s="1">
-        <v>100700</v>
+        <v>100603</v>
       </c>
     </row>
     <row r="909" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A909" s="1">
-        <v>100701</v>
+        <v>100604</v>
       </c>
     </row>
     <row r="910" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A910" s="1">
-        <v>100702</v>
+        <v>100605</v>
       </c>
     </row>
     <row r="911" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A911" s="1">
-        <v>100703</v>
+        <v>100606</v>
       </c>
     </row>
     <row r="912" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A912" s="1">
-        <v>100704</v>
+        <v>100607</v>
       </c>
     </row>
     <row r="913" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A913" s="1">
-        <v>100705</v>
+        <v>100608</v>
       </c>
     </row>
     <row r="914" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A914" s="1">
-        <v>100706</v>
+        <v>100609</v>
       </c>
     </row>
     <row r="915" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A915" s="1">
-        <v>100707</v>
+        <v>100610</v>
       </c>
     </row>
     <row r="916" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A916" s="1">
-        <v>100708</v>
+        <v>100611</v>
       </c>
     </row>
     <row r="917" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A917" s="1">
-        <v>100709</v>
+        <v>100612</v>
       </c>
     </row>
     <row r="918" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A918" s="1">
-        <v>100710</v>
+        <v>100613</v>
       </c>
     </row>
     <row r="919" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A919" s="1">
-        <v>100711</v>
+        <v>100614</v>
       </c>
     </row>
     <row r="920" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A920" s="1">
-        <v>100712</v>
+        <v>100615</v>
       </c>
     </row>
     <row r="921" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A921" s="1">
-        <v>100713</v>
+        <v>100616</v>
       </c>
     </row>
     <row r="922" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A922" s="1">
-        <v>100714</v>
+        <v>100617</v>
       </c>
     </row>
     <row r="923" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A923" s="1">
-        <v>100715</v>
+        <v>100618</v>
       </c>
     </row>
     <row r="924" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A924" s="1">
-        <v>100716</v>
+        <v>100619</v>
       </c>
     </row>
     <row r="925" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A925" s="1">
-        <v>100717</v>
+        <v>100620</v>
       </c>
     </row>
     <row r="926" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A926" s="1">
-        <v>100718</v>
+        <v>100621</v>
       </c>
     </row>
     <row r="927" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A927" s="1">
-        <v>100719</v>
+        <v>100622</v>
       </c>
     </row>
     <row r="928" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A928" s="1">
-        <v>100720</v>
+        <v>100623</v>
       </c>
     </row>
     <row r="929" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A929" s="1">
-        <v>100721</v>
+        <v>100624</v>
       </c>
     </row>
     <row r="930" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A930" s="1">
-        <v>100722</v>
+        <v>100625</v>
       </c>
     </row>
     <row r="931" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A931" s="1">
-        <v>100723</v>
+        <v>100626</v>
       </c>
     </row>
     <row r="932" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A932" s="1">
-        <v>100724</v>
+        <v>100627</v>
       </c>
     </row>
     <row r="933" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A933" s="1">
-        <v>100725</v>
+        <v>100628</v>
       </c>
     </row>
     <row r="934" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A934" s="1">
-        <v>100726</v>
+        <v>100629</v>
       </c>
     </row>
     <row r="935" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A935" s="1">
-        <v>100727</v>
+        <v>100630</v>
       </c>
     </row>
     <row r="936" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A936" s="1">
-        <v>100728</v>
+        <v>100631</v>
       </c>
     </row>
     <row r="937" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A937" s="1">
-        <v>100729</v>
+        <v>100632</v>
       </c>
     </row>
     <row r="938" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A938" s="1">
-        <v>100730</v>
+        <v>100633</v>
       </c>
     </row>
     <row r="939" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A939" s="1">
-        <v>100731</v>
+        <v>100634</v>
       </c>
     </row>
     <row r="940" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A940" s="1">
-        <v>100732</v>
+        <v>100635</v>
       </c>
     </row>
     <row r="941" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A941" s="1">
-        <v>100733</v>
+        <v>100636</v>
       </c>
     </row>
     <row r="942" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A942" s="1">
-        <v>100734</v>
+        <v>100637</v>
       </c>
     </row>
     <row r="943" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A943" s="1">
-        <v>100735</v>
+        <v>100638</v>
       </c>
     </row>
     <row r="944" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A944" s="1">
-        <v>100736</v>
+        <v>100639</v>
       </c>
     </row>
     <row r="945" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A945" s="1">
-        <v>100737</v>
+        <v>100640</v>
       </c>
     </row>
     <row r="946" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A946" s="1">
-        <v>100738</v>
+        <v>100641</v>
       </c>
     </row>
     <row r="947" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A947" s="1">
-        <v>100739</v>
+        <v>100642</v>
       </c>
     </row>
     <row r="948" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A948" s="1">
-        <v>100740</v>
+        <v>100643</v>
       </c>
     </row>
     <row r="949" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A949" s="1">
-        <v>100741</v>
+        <v>100644</v>
       </c>
     </row>
     <row r="950" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A950" s="1">
-        <v>100742</v>
+        <v>100645</v>
       </c>
     </row>
     <row r="951" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A951" s="1">
-        <v>100743</v>
+        <v>100646</v>
       </c>
     </row>
     <row r="952" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A952" s="1">
-        <v>100744</v>
+        <v>100647</v>
       </c>
     </row>
     <row r="953" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A953" s="1">
-        <v>100745</v>
+        <v>100648</v>
       </c>
     </row>
     <row r="954" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A954" s="1">
-        <v>100746</v>
+        <v>100649</v>
       </c>
     </row>
     <row r="955" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A955" s="1">
-        <v>100747</v>
+        <v>100650</v>
       </c>
     </row>
     <row r="956" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A956" s="1">
-        <v>100748</v>
+        <v>100651</v>
       </c>
     </row>
     <row r="957" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A957" s="1">
-        <v>100749</v>
+        <v>100652</v>
       </c>
     </row>
     <row r="958" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A958" s="1">
-        <v>100750</v>
+        <v>100653</v>
       </c>
     </row>
     <row r="959" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A959" s="1">
-        <v>100751</v>
+        <v>100654</v>
       </c>
     </row>
     <row r="960" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A960" s="1">
-        <v>100752</v>
+        <v>100655</v>
       </c>
     </row>
     <row r="961" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A961" s="1">
-        <v>100753</v>
+        <v>100656</v>
       </c>
     </row>
     <row r="962" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A962" s="1">
-        <v>100754</v>
+        <v>100657</v>
       </c>
     </row>
     <row r="963" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A963" s="1">
-        <v>100755</v>
+        <v>100658</v>
       </c>
     </row>
     <row r="964" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A964" s="1">
-        <v>100756</v>
+        <v>100659</v>
       </c>
     </row>
     <row r="965" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A965" s="1">
-        <v>100757</v>
+        <v>100660</v>
       </c>
     </row>
     <row r="966" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A966" s="1">
-        <v>100758</v>
+        <v>100661</v>
       </c>
     </row>
     <row r="967" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A967" s="1">
-        <v>100759</v>
+        <v>100662</v>
       </c>
     </row>
     <row r="968" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A968" s="1">
-        <v>100760</v>
+        <v>100663</v>
       </c>
     </row>
     <row r="969" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A969" s="1">
-        <v>100761</v>
+        <v>100664</v>
       </c>
     </row>
     <row r="970" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A970" s="1">
-        <v>100762</v>
+        <v>100665</v>
       </c>
     </row>
     <row r="971" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A971" s="1">
-        <v>100763</v>
+        <v>100666</v>
       </c>
     </row>
     <row r="972" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A972" s="1">
-        <v>100764</v>
+        <v>100667</v>
       </c>
     </row>
     <row r="973" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A973" s="1">
-        <v>100765</v>
+        <v>100668</v>
       </c>
     </row>
     <row r="974" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A974" s="1">
-        <v>100766</v>
+        <v>100669</v>
       </c>
     </row>
     <row r="975" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A975" s="1">
-        <v>100767</v>
+        <v>100670</v>
       </c>
     </row>
     <row r="976" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A976" s="1">
-        <v>100768</v>
+        <v>100671</v>
       </c>
     </row>
     <row r="977" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A977" s="1">
-        <v>100769</v>
+        <v>100672</v>
       </c>
     </row>
     <row r="978" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A978" s="1">
-        <v>100770</v>
+        <v>100673</v>
       </c>
     </row>
     <row r="979" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A979" s="1">
-        <v>100771</v>
+        <v>100674</v>
       </c>
     </row>
     <row r="980" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A980" s="1">
-        <v>100772</v>
+        <v>100675</v>
       </c>
     </row>
     <row r="981" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A981" s="1">
-        <v>100773</v>
+        <v>100676</v>
       </c>
     </row>
     <row r="982" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A982" s="1">
-        <v>100774</v>
+        <v>100677</v>
       </c>
     </row>
     <row r="983" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A983" s="1">
-        <v>100775</v>
+        <v>100678</v>
       </c>
     </row>
     <row r="984" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A984" s="1">
-        <v>100776</v>
+        <v>100679</v>
       </c>
     </row>
     <row r="985" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A985" s="1">
-        <v>100777</v>
+        <v>100680</v>
       </c>
     </row>
     <row r="986" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A986" s="1">
-        <v>100778</v>
+        <v>100681</v>
       </c>
     </row>
     <row r="987" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A987" s="1">
-        <v>100779</v>
+        <v>100682</v>
       </c>
     </row>
     <row r="988" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A988" s="1">
-        <v>100780</v>
+        <v>100683</v>
       </c>
     </row>
     <row r="989" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A989" s="1">
-        <v>100781</v>
+        <v>100684</v>
       </c>
     </row>
     <row r="990" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A990" s="1">
-        <v>100782</v>
+        <v>100685</v>
       </c>
     </row>
     <row r="991" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A991" s="1">
-        <v>100783</v>
+        <v>100686</v>
       </c>
     </row>
     <row r="992" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A992" s="1">
-        <v>100784</v>
+        <v>100687</v>
       </c>
     </row>
     <row r="993" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A993" s="1">
-        <v>100785</v>
+        <v>100688</v>
       </c>
     </row>
     <row r="994" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A994" s="1">
-        <v>100786</v>
+        <v>100689</v>
       </c>
     </row>
     <row r="995" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A995" s="1">
-        <v>100787</v>
+        <v>100690</v>
       </c>
     </row>
     <row r="996" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A996" s="1">
-        <v>100788</v>
+        <v>100691</v>
       </c>
     </row>
     <row r="997" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A997" s="1">
-        <v>100789</v>
+        <v>100692</v>
       </c>
     </row>
     <row r="998" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A998" s="1">
-        <v>100790</v>
+        <v>100693</v>
       </c>
     </row>
     <row r="999" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A999" s="1">
-        <v>100791</v>
+        <v>100694</v>
       </c>
     </row>
     <row r="1000" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1000" s="1">
-        <v>100792</v>
+        <v>100695</v>
       </c>
     </row>
     <row r="1001" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1001" s="1">
-        <v>100793</v>
+        <v>100696</v>
       </c>
     </row>
     <row r="1002" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1002" s="1">
-        <v>100794</v>
+        <v>100697</v>
       </c>
     </row>
     <row r="1003" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1003" s="1">
-        <v>100795</v>
+        <v>100698</v>
       </c>
     </row>
     <row r="1004" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1004" s="1">
-        <v>100796</v>
+        <v>100699</v>
       </c>
     </row>
     <row r="1005" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1005" s="1">
-        <v>100797</v>
+        <v>100700</v>
       </c>
     </row>
     <row r="1006" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1006" s="1">
-        <v>100798</v>
+        <v>100701</v>
       </c>
     </row>
     <row r="1007" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1007" s="1">
-        <v>100799</v>
+        <v>100702</v>
       </c>
     </row>
     <row r="1008" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1008" s="1">
-        <v>100800</v>
+        <v>100703</v>
       </c>
     </row>
     <row r="1009" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1009" s="1">
-        <v>100801</v>
+        <v>100704</v>
       </c>
     </row>
     <row r="1010" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1010" s="1">
-        <v>100802</v>
+        <v>100705</v>
       </c>
     </row>
     <row r="1011" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1011" s="1">
-        <v>100803</v>
+        <v>100706</v>
       </c>
     </row>
     <row r="1012" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1012" s="1">
-        <v>100804</v>
+        <v>100707</v>
       </c>
     </row>
     <row r="1013" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1013" s="1">
-        <v>100805</v>
+        <v>100708</v>
       </c>
     </row>
     <row r="1014" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1014" s="1">
-        <v>100806</v>
+        <v>100709</v>
       </c>
     </row>
     <row r="1015" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1015" s="1">
-        <v>100807</v>
+        <v>100710</v>
       </c>
     </row>
     <row r="1016" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1016" s="1">
-        <v>100808</v>
+        <v>100711</v>
       </c>
     </row>
     <row r="1017" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1017" s="1">
-        <v>100809</v>
+        <v>100712</v>
       </c>
     </row>
     <row r="1018" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1018" s="1">
-        <v>100810</v>
+        <v>100713</v>
       </c>
     </row>
     <row r="1019" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1019" s="1">
-        <v>100811</v>
+        <v>100714</v>
       </c>
     </row>
     <row r="1020" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1020" s="1">
-        <v>100812</v>
+        <v>100715</v>
       </c>
     </row>
     <row r="1021" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1021" s="1">
-        <v>100813</v>
+        <v>100716</v>
       </c>
     </row>
     <row r="1022" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1022" s="1">
-        <v>100814</v>
+        <v>100717</v>
       </c>
     </row>
     <row r="1023" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1023" s="1">
-        <v>100815</v>
+        <v>100718</v>
       </c>
     </row>
     <row r="1024" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1024" s="1">
-        <v>100816</v>
+        <v>100719</v>
       </c>
     </row>
     <row r="1025" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1025" s="1">
-        <v>100817</v>
+        <v>100720</v>
       </c>
     </row>
     <row r="1026" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1026" s="1">
-        <v>100818</v>
+        <v>100721</v>
       </c>
     </row>
     <row r="1027" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1027" s="1">
-        <v>100819</v>
+        <v>100722</v>
       </c>
     </row>
     <row r="1028" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1028" s="1">
-        <v>100820</v>
+        <v>100723</v>
       </c>
     </row>
     <row r="1029" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1029" s="1">
-        <v>100821</v>
+        <v>100724</v>
       </c>
     </row>
     <row r="1030" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1030" s="1">
-        <v>100822</v>
+        <v>100725</v>
       </c>
     </row>
     <row r="1031" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1031" s="1">
-        <v>100823</v>
+        <v>100726</v>
       </c>
     </row>
     <row r="1032" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1032" s="1">
-        <v>100824</v>
+        <v>100727</v>
       </c>
     </row>
     <row r="1033" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1033" s="1">
-        <v>100825</v>
+        <v>100728</v>
       </c>
     </row>
     <row r="1034" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1034" s="1">
-        <v>100826</v>
+        <v>100729</v>
       </c>
     </row>
     <row r="1035" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1035" s="1">
-        <v>100827</v>
+        <v>100730</v>
       </c>
     </row>
     <row r="1036" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1036" s="1">
-        <v>100828</v>
+        <v>100731</v>
       </c>
     </row>
     <row r="1037" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1037" s="1">
-        <v>100829</v>
+        <v>100732</v>
       </c>
     </row>
     <row r="1038" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1038" s="1">
-        <v>100830</v>
+        <v>100733</v>
       </c>
     </row>
     <row r="1039" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1039" s="1">
-        <v>100831</v>
+        <v>100734</v>
       </c>
     </row>
     <row r="1040" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1040" s="1">
-        <v>100832</v>
+        <v>100735</v>
       </c>
     </row>
     <row r="1041" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1041" s="1">
-        <v>100833</v>
+        <v>100736</v>
       </c>
     </row>
     <row r="1042" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1042" s="1">
-        <v>100834</v>
+        <v>100737</v>
       </c>
     </row>
     <row r="1043" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1043" s="1">
-        <v>100835</v>
+        <v>100738</v>
       </c>
     </row>
     <row r="1044" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1044" s="1">
-        <v>100836</v>
+        <v>100739</v>
       </c>
     </row>
     <row r="1045" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1045" s="1">
-        <v>100837</v>
+        <v>100740</v>
       </c>
     </row>
     <row r="1046" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1046" s="1">
-        <v>100838</v>
+        <v>100741</v>
       </c>
     </row>
     <row r="1047" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1047" s="1">
-        <v>100839</v>
+        <v>100742</v>
       </c>
     </row>
     <row r="1048" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1048" s="1">
-        <v>100840</v>
+        <v>100743</v>
       </c>
     </row>
     <row r="1049" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1049" s="1">
-        <v>100841</v>
+        <v>100744</v>
       </c>
     </row>
     <row r="1050" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1050" s="1">
-        <v>100842</v>
+        <v>100745</v>
       </c>
     </row>
     <row r="1051" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1051" s="1">
-        <v>100843</v>
+        <v>100746</v>
       </c>
     </row>
     <row r="1052" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1052" s="1">
-        <v>100844</v>
+        <v>100747</v>
       </c>
     </row>
     <row r="1053" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1053" s="1">
-        <v>100845</v>
+        <v>100748</v>
       </c>
     </row>
     <row r="1054" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1054" s="1">
-        <v>100846</v>
+        <v>100749</v>
       </c>
     </row>
     <row r="1055" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1055" s="1">
-        <v>100847</v>
+        <v>100750</v>
       </c>
     </row>
     <row r="1056" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1056" s="1">
-        <v>100848</v>
+        <v>100751</v>
       </c>
     </row>
     <row r="1057" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1057" s="1">
-        <v>100849</v>
+        <v>100752</v>
       </c>
     </row>
     <row r="1058" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1058" s="1">
-        <v>100850</v>
+        <v>100753</v>
       </c>
     </row>
     <row r="1059" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1059" s="1">
-        <v>100851</v>
+        <v>100754</v>
       </c>
     </row>
     <row r="1060" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1060" s="1">
-        <v>100852</v>
+        <v>100755</v>
       </c>
     </row>
     <row r="1061" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1061" s="1">
-        <v>100853</v>
+        <v>100756</v>
       </c>
     </row>
     <row r="1062" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1062" s="1">
-        <v>100854</v>
+        <v>100757</v>
       </c>
     </row>
     <row r="1063" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1063" s="1">
-        <v>100855</v>
+        <v>100758</v>
       </c>
     </row>
     <row r="1064" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1064" s="1">
-        <v>100856</v>
+        <v>100759</v>
       </c>
     </row>
     <row r="1065" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1065" s="1">
-        <v>100857</v>
+        <v>100760</v>
       </c>
     </row>
     <row r="1066" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1066" s="1">
-        <v>100858</v>
+        <v>100761</v>
       </c>
     </row>
     <row r="1067" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1067" s="1">
-        <v>100859</v>
+        <v>100762</v>
       </c>
     </row>
     <row r="1068" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1068" s="1">
-        <v>100860</v>
+        <v>100763</v>
       </c>
     </row>
     <row r="1069" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1069" s="1">
-        <v>100861</v>
+        <v>100764</v>
       </c>
     </row>
     <row r="1070" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1070" s="1">
-        <v>100862</v>
+        <v>100765</v>
       </c>
     </row>
     <row r="1071" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1071" s="1">
-        <v>100863</v>
+        <v>100766</v>
       </c>
     </row>
     <row r="1072" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1072" s="1">
-        <v>100864</v>
+        <v>100767</v>
       </c>
     </row>
     <row r="1073" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1073" s="1">
-        <v>100865</v>
+        <v>100768</v>
       </c>
     </row>
     <row r="1074" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1074" s="1">
-        <v>100866</v>
+        <v>100769</v>
       </c>
     </row>
     <row r="1075" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1075" s="1">
-        <v>100867</v>
+        <v>100770</v>
       </c>
     </row>
     <row r="1076" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1076" s="1">
-        <v>100868</v>
+        <v>100771</v>
       </c>
     </row>
     <row r="1077" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1077" s="1">
-        <v>100869</v>
+        <v>100772</v>
       </c>
     </row>
     <row r="1078" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1078" s="1">
-        <v>100870</v>
+        <v>100773</v>
       </c>
     </row>
     <row r="1079" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1079" s="1">
-        <v>100871</v>
+        <v>100774</v>
       </c>
     </row>
     <row r="1080" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1080" s="1">
-        <v>100872</v>
+        <v>100775</v>
       </c>
     </row>
     <row r="1081" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1081" s="1">
-        <v>100873</v>
+        <v>100776</v>
       </c>
     </row>
     <row r="1082" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1082" s="1">
-        <v>100874</v>
+        <v>100777</v>
       </c>
     </row>
     <row r="1083" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1083" s="1">
-        <v>100875</v>
+        <v>100778</v>
       </c>
     </row>
     <row r="1084" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1084" s="1">
-        <v>100876</v>
+        <v>100779</v>
       </c>
     </row>
     <row r="1085" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1085" s="1">
-        <v>100877</v>
+        <v>100780</v>
       </c>
     </row>
     <row r="1086" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1086" s="1">
-        <v>100878</v>
+        <v>100781</v>
       </c>
     </row>
     <row r="1087" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1087" s="1">
-        <v>100879</v>
+        <v>100782</v>
       </c>
     </row>
     <row r="1088" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1088" s="1">
-        <v>100880</v>
+        <v>100783</v>
       </c>
     </row>
     <row r="1089" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1089" s="1">
-        <v>100881</v>
+        <v>100784</v>
       </c>
     </row>
     <row r="1090" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1090" s="1">
-        <v>100882</v>
+        <v>100785</v>
       </c>
     </row>
     <row r="1091" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1091" s="1">
-        <v>100883</v>
+        <v>100786</v>
       </c>
     </row>
     <row r="1092" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1092" s="1">
-        <v>100884</v>
+        <v>100787</v>
       </c>
     </row>
     <row r="1093" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1093" s="1">
-        <v>100885</v>
+        <v>100788</v>
       </c>
     </row>
     <row r="1094" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1094" s="1">
-        <v>100886</v>
+        <v>100789</v>
       </c>
     </row>
     <row r="1095" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1095" s="1">
-        <v>100887</v>
+        <v>100790</v>
       </c>
     </row>
     <row r="1096" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1096" s="1">
-        <v>100888</v>
+        <v>100791</v>
       </c>
     </row>
     <row r="1097" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1097" s="1">
-        <v>100889</v>
+        <v>100792</v>
       </c>
     </row>
     <row r="1098" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1098" s="1">
-        <v>100890</v>
+        <v>100793</v>
       </c>
     </row>
     <row r="1099" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1099" s="1">
-        <v>100891</v>
+        <v>100794</v>
       </c>
     </row>
     <row r="1100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1100" s="1">
-        <v>100892</v>
+        <v>100795</v>
       </c>
     </row>
     <row r="1101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1101" s="1">
-        <v>100893</v>
+        <v>100796</v>
       </c>
     </row>
     <row r="1102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1102" s="1">
-        <v>100894</v>
+        <v>100797</v>
       </c>
     </row>
     <row r="1103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1103" s="1">
-        <v>100895</v>
+        <v>100798</v>
       </c>
     </row>
     <row r="1104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1104" s="1">
-        <v>100896</v>
+        <v>100799</v>
       </c>
     </row>
     <row r="1105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1105" s="1">
-        <v>100897</v>
+        <v>100800</v>
       </c>
     </row>
     <row r="1106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1106" s="1">
-        <v>100898</v>
+        <v>100801</v>
       </c>
     </row>
     <row r="1107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1107" s="1">
-        <v>100899</v>
+        <v>100802</v>
       </c>
     </row>
     <row r="1108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1108" s="1">
-        <v>100900</v>
+        <v>100803</v>
       </c>
     </row>
     <row r="1109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1109" s="1">
-        <v>100901</v>
+        <v>100804</v>
       </c>
     </row>
     <row r="1110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1110" s="1">
-        <v>100902</v>
+        <v>100805</v>
       </c>
     </row>
     <row r="1111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1111" s="1">
-        <v>100903</v>
+        <v>100806</v>
       </c>
     </row>
     <row r="1112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1112" s="1">
-        <v>100904</v>
+        <v>100807</v>
       </c>
     </row>
     <row r="1113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1113" s="1">
-        <v>100905</v>
+        <v>100808</v>
       </c>
     </row>
     <row r="1114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1114" s="1">
-        <v>100906</v>
+        <v>100809</v>
       </c>
     </row>
     <row r="1115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1115" s="1">
-        <v>100907</v>
+        <v>100810</v>
       </c>
     </row>
     <row r="1116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1116" s="1">
-        <v>100908</v>
+        <v>100811</v>
       </c>
     </row>
     <row r="1117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1117" s="1">
-        <v>100909</v>
+        <v>100812</v>
       </c>
     </row>
     <row r="1118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1118" s="1">
-        <v>100910</v>
+        <v>100813</v>
       </c>
     </row>
     <row r="1119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1119" s="1">
-        <v>100911</v>
+        <v>100814</v>
       </c>
     </row>
     <row r="1120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1120" s="1">
-        <v>100912</v>
+        <v>100815</v>
       </c>
     </row>
     <row r="1121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1121" s="1">
-        <v>100913</v>
+        <v>100816</v>
       </c>
     </row>
     <row r="1122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1122" s="1">
-        <v>100914</v>
+        <v>100817</v>
       </c>
     </row>
     <row r="1123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1123" s="1">
-        <v>100915</v>
+        <v>100818</v>
       </c>
     </row>
     <row r="1124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1124" s="1">
-        <v>100916</v>
+        <v>100819</v>
       </c>
     </row>
     <row r="1125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1125" s="1">
-        <v>100917</v>
+        <v>100820</v>
       </c>
     </row>
     <row r="1126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1126" s="1">
-        <v>100918</v>
+        <v>100821</v>
       </c>
     </row>
     <row r="1127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1127" s="1">
-        <v>100919</v>
+        <v>100822</v>
       </c>
     </row>
     <row r="1128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1128" s="1">
-        <v>100920</v>
+        <v>100823</v>
       </c>
     </row>
     <row r="1129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1129" s="1">
-        <v>100921</v>
+        <v>100824</v>
       </c>
     </row>
     <row r="1130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1130" s="1">
-        <v>100922</v>
+        <v>100825</v>
       </c>
     </row>
     <row r="1131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1131" s="1">
-        <v>100923</v>
+        <v>100826</v>
       </c>
     </row>
     <row r="1132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1132" s="1">
-        <v>100924</v>
+        <v>100827</v>
       </c>
     </row>
     <row r="1133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1133" s="1">
-        <v>100925</v>
+        <v>100828</v>
       </c>
     </row>
     <row r="1134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1134" s="1">
-        <v>100926</v>
+        <v>100829</v>
       </c>
     </row>
     <row r="1135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1135" s="1">
-        <v>100927</v>
+        <v>100830</v>
       </c>
     </row>
     <row r="1136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1136" s="1">
-        <v>100928</v>
+        <v>100831</v>
       </c>
     </row>
     <row r="1137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1137" s="1">
-        <v>100929</v>
+        <v>100832</v>
       </c>
     </row>
     <row r="1138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1138" s="1">
-        <v>100930</v>
+        <v>100833</v>
       </c>
     </row>
     <row r="1139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1139" s="1">
-        <v>100931</v>
+        <v>100834</v>
       </c>
     </row>
     <row r="1140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1140" s="1">
-        <v>100932</v>
+        <v>100835</v>
       </c>
     </row>
     <row r="1141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1141" s="1">
-        <v>100933</v>
+        <v>100836</v>
       </c>
     </row>
     <row r="1142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1142" s="1">
-        <v>100934</v>
+        <v>100837</v>
       </c>
     </row>
     <row r="1143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1143" s="1">
-        <v>100935</v>
+        <v>100838</v>
       </c>
     </row>
     <row r="1144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1144" s="1">
-        <v>100936</v>
+        <v>100839</v>
       </c>
     </row>
     <row r="1145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1145" s="1">
-        <v>100937</v>
+        <v>100840</v>
       </c>
     </row>
     <row r="1146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1146" s="1">
-        <v>100938</v>
+        <v>100841</v>
       </c>
     </row>
     <row r="1147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1147" s="1">
-        <v>100939</v>
+        <v>100842</v>
       </c>
     </row>
     <row r="1148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1148" s="1">
-        <v>100940</v>
+        <v>100843</v>
       </c>
     </row>
     <row r="1149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1149" s="1">
-        <v>100941</v>
+        <v>100844</v>
       </c>
     </row>
     <row r="1150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1150" s="1">
-        <v>100942</v>
+        <v>100845</v>
       </c>
     </row>
     <row r="1151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1151" s="1">
-        <v>100943</v>
+        <v>100846</v>
       </c>
     </row>
     <row r="1152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1152" s="1">
-        <v>100944</v>
+        <v>100847</v>
       </c>
     </row>
     <row r="1153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1153" s="1">
-        <v>100945</v>
+        <v>100848</v>
       </c>
     </row>
     <row r="1154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1154" s="1">
-        <v>100946</v>
+        <v>100849</v>
       </c>
     </row>
     <row r="1155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1155" s="1">
-        <v>100947</v>
+        <v>100850</v>
       </c>
     </row>
     <row r="1156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1156" s="1">
-        <v>100948</v>
+        <v>100851</v>
       </c>
     </row>
     <row r="1157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1157" s="1">
-        <v>100949</v>
+        <v>100852</v>
       </c>
     </row>
     <row r="1158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1158" s="1">
-        <v>100950</v>
+        <v>100853</v>
       </c>
     </row>
     <row r="1159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1159" s="1">
-        <v>100951</v>
+        <v>100854</v>
       </c>
     </row>
     <row r="1160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1160" s="1">
-        <v>100952</v>
+        <v>100855</v>
       </c>
     </row>
     <row r="1161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1161" s="1">
-        <v>100953</v>
+        <v>100856</v>
       </c>
     </row>
     <row r="1162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1162" s="1">
-        <v>100954</v>
+        <v>100857</v>
       </c>
     </row>
     <row r="1163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1163" s="1">
-        <v>100955</v>
+        <v>100858</v>
       </c>
     </row>
     <row r="1164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1164" s="1">
-        <v>100956</v>
+        <v>100859</v>
       </c>
     </row>
     <row r="1165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1165" s="1">
-        <v>100957</v>
+        <v>100860</v>
       </c>
     </row>
     <row r="1166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1166" s="1">
-        <v>100958</v>
+        <v>100861</v>
       </c>
     </row>
     <row r="1167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1167" s="1">
-        <v>100959</v>
+        <v>100862</v>
       </c>
     </row>
     <row r="1168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1168" s="1">
-        <v>100960</v>
+        <v>100863</v>
       </c>
     </row>
     <row r="1169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1169" s="1">
-        <v>100961</v>
+        <v>100864</v>
       </c>
     </row>
     <row r="1170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1170" s="1">
+        <v>100865</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1171" s="1">
+        <v>100866</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1172" s="1">
+        <v>100867</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1173" s="1">
+        <v>100868</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1174" s="1">
+        <v>100869</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1175" s="1">
+        <v>100870</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1176" s="1">
+        <v>100871</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1177" s="1">
+        <v>100872</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1178" s="1">
+        <v>100873</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1179" s="1">
+        <v>100874</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1180" s="1">
+        <v>100875</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1181" s="1">
+        <v>100876</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1182" s="1">
+        <v>100877</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1183" s="1">
+        <v>100878</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1184" s="1">
+        <v>100879</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1185" s="1">
+        <v>100880</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1186" s="1">
+        <v>100881</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1187" s="1">
+        <v>100882</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1188" s="1">
+        <v>100883</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1189" s="1">
+        <v>100884</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1190" s="1">
+        <v>100885</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1191" s="1">
+        <v>100886</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1192" s="1">
+        <v>100887</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1193" s="1">
+        <v>100888</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1194" s="1">
+        <v>100889</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1195" s="1">
+        <v>100890</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1196" s="1">
+        <v>100891</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1197" s="1">
+        <v>100892</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1198" s="1">
+        <v>100893</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1199" s="1">
+        <v>100894</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1200" s="1">
+        <v>100895</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1201" s="1">
+        <v>100896</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1202" s="1">
+        <v>100897</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1203" s="1">
+        <v>100898</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1204" s="1">
+        <v>100899</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1205" s="1">
+        <v>100900</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1206" s="1">
+        <v>100901</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1207" s="1">
+        <v>100902</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1208" s="1">
+        <v>100903</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1209" s="1">
+        <v>100904</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1210" s="1">
+        <v>100905</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1211" s="1">
+        <v>100906</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1212" s="1">
+        <v>100907</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1213" s="1">
+        <v>100908</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1214" s="1">
+        <v>100909</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1215" s="1">
+        <v>100910</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1216" s="1">
+        <v>100911</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1217" s="1">
+        <v>100912</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1218" s="1">
+        <v>100913</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1219" s="1">
+        <v>100914</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1220" s="1">
+        <v>100915</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1221" s="1">
+        <v>100916</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1222" s="1">
+        <v>100917</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1223" s="1">
+        <v>100918</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1224" s="1">
+        <v>100919</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1225" s="1">
+        <v>100920</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1226" s="1">
+        <v>100921</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1227" s="1">
+        <v>100922</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1228" s="1">
+        <v>100923</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1229" s="1">
+        <v>100924</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1230" s="1">
+        <v>100925</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1231" s="1">
+        <v>100926</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1232" s="1">
+        <v>100927</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1233" s="1">
+        <v>100928</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1234" s="1">
+        <v>100929</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1235" s="1">
+        <v>100930</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1236" s="1">
+        <v>100931</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1237" s="1">
+        <v>100932</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1238" s="1">
+        <v>100933</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1239" s="1">
+        <v>100934</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1240" s="1">
+        <v>100935</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1241" s="1">
+        <v>100936</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1242" s="1">
+        <v>100937</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1243" s="1">
+        <v>100938</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1244" s="1">
+        <v>100939</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1245" s="1">
+        <v>100940</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1246" s="1">
+        <v>100941</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1247" s="1">
+        <v>100942</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1248" s="1">
+        <v>100943</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1249" s="1">
+        <v>100944</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1250" s="1">
+        <v>100945</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1251" s="1">
+        <v>100946</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1252" s="1">
+        <v>100947</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1253" s="1">
+        <v>100948</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1254" s="1">
+        <v>100949</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1255" s="1">
+        <v>100950</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1256" s="1">
+        <v>100951</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1257" s="1">
+        <v>100952</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1258" s="1">
+        <v>100953</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1259" s="1">
+        <v>100954</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1260" s="1">
+        <v>100955</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1261" s="1">
+        <v>100956</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1262" s="1">
+        <v>100957</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1263" s="1">
+        <v>100958</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1264" s="1">
+        <v>100959</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1265" s="1">
+        <v>100960</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1266" s="1">
+        <v>100961</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1267" s="1">
         <v>100962</v>
       </c>
     </row>

--- a/database.xlsx
+++ b/database.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1244"/>
+  <dimension ref="A1:E1243"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -21552,26 +21552,9 @@
         <v/>
       </c>
     </row>
-    <row r="1244">
-      <c r="A1244" t="str">
-        <v>99995</v>
-      </c>
-      <c r="B1244" t="str">
-        <v>СТАНДАРТ</v>
-      </c>
-      <c r="C1244" t="str">
-        <v>08.06.2026</v>
-      </c>
-      <c r="D1244" t="str">
-        <v/>
-      </c>
-      <c r="E1244" t="str">
-        <v>2026-06-08T18:05:03.590Z</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E1244"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E1243"/>
   </ignoredErrors>
 </worksheet>
 </file>